--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>130356940</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>130357215</v>
       </c>
       <c r="B4" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +999,7 @@
         <v>130357384</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         <v>130357520</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,12 +1198,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
         <v>130356906</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,12 +1305,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130356940</v>
       </c>
       <c r="B3" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130357215</v>
       </c>
       <c r="B4" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130357384</v>
       </c>
       <c r="B5" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130357520</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130356906</v>
       </c>
       <c r="B7" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130356940</v>
       </c>
       <c r="B3" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130357215</v>
       </c>
       <c r="B4" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130357384</v>
       </c>
       <c r="B5" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130357520</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130356906</v>
       </c>
       <c r="B7" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130356940</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130357215</v>
       </c>
       <c r="B4" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130357384</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130357520</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130356906</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92483</v>
+        <v>92496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83199</v>
+        <v>83200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130356940</v>
       </c>
       <c r="B3" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130357215</v>
       </c>
       <c r="B4" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130357384</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130357520</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130356906</v>
       </c>
       <c r="B7" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130357350</v>
       </c>
       <c r="B2" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130356940</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130357215</v>
       </c>
       <c r="B4" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130357384</v>
       </c>
       <c r="B5" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130357520</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130356906</v>
       </c>
       <c r="B7" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130357102</v>
       </c>
       <c r="B8" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130357215</v>
+        <v>130357384</v>
       </c>
       <c r="B4" t="n">
         <v>80326</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485765</v>
+        <v>485781</v>
       </c>
       <c r="R4" t="n">
-        <v>6939316</v>
+        <v>6939306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130357384</v>
+        <v>130357215</v>
       </c>
       <c r="B5" t="n">
         <v>80326</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485781</v>
+        <v>485765</v>
       </c>
       <c r="R5" t="n">
-        <v>6939306</v>
+        <v>6939316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130357384</v>
+        <v>130357215</v>
       </c>
       <c r="B4" t="n">
         <v>80326</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485781</v>
+        <v>485765</v>
       </c>
       <c r="R4" t="n">
-        <v>6939306</v>
+        <v>6939316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130357215</v>
+        <v>130357384</v>
       </c>
       <c r="B5" t="n">
         <v>80326</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485765</v>
+        <v>485781</v>
       </c>
       <c r="R5" t="n">
-        <v>6939316</v>
+        <v>6939306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 57276-2025 artfynd.xlsx
+++ b/artfynd/A 57276-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130357350</v>
+        <v>130356809</v>
       </c>
       <c r="B2" t="n">
-        <v>83201</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485779</v>
+        <v>485662</v>
       </c>
       <c r="R2" t="n">
-        <v>6939306</v>
+        <v>6939425</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130356940</v>
+        <v>130357102</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485667</v>
+        <v>485729</v>
       </c>
       <c r="R3" t="n">
-        <v>6939369</v>
+        <v>6939345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130357215</v>
+        <v>130357520</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485765</v>
+        <v>485852</v>
       </c>
       <c r="R4" t="n">
-        <v>6939316</v>
+        <v>6939336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130357384</v>
+        <v>130357350</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485781</v>
+        <v>485779</v>
       </c>
       <c r="R5" t="n">
         <v>6939306</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130357520</v>
+        <v>130356906</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485852</v>
+        <v>485679</v>
       </c>
       <c r="R6" t="n">
-        <v>6939336</v>
+        <v>6939384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130356906</v>
+        <v>130356940</v>
       </c>
       <c r="B7" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485679</v>
+        <v>485667</v>
       </c>
       <c r="R7" t="n">
-        <v>6939384</v>
+        <v>6939369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130357102</v>
+        <v>130357215</v>
       </c>
       <c r="B8" t="n">
-        <v>92506</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485729</v>
+        <v>485765</v>
       </c>
       <c r="R8" t="n">
-        <v>6939345</v>
+        <v>6939316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,6 +1421,337 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130357384</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storfloberget, Storfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>485781</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6939306</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130608723</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>485644</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6939283</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På grankvistar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130356714</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>485656</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6939423</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
